--- a/data/vzor_cenik_Zetta90_ral.xlsx
+++ b/data/vzor_cenik_Zetta90_ral.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="32760" yWindow="32760" windowWidth="18030" windowHeight="5625"/>
+    <workbookView windowWidth="28800" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="venkovní žaluzie" sheetId="3" r:id="rId1"/>
@@ -161,7 +161,7 @@
     <t>Montáž + doprava</t>
   </si>
   <si>
-    <t xml:space="preserve">Doprava </t>
+    <t>Doprava (1x zaměření 1x montáž)</t>
   </si>
   <si>
     <t xml:space="preserve">Montáž </t>
@@ -227,13 +227,11 @@
     <font>
       <sz val="12"/>
       <name val="Times New Roman CE"/>
-      <family val="1"/>
       <charset val="238"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Times New Roman CE"/>
-      <family val="1"/>
       <charset val="238"/>
     </font>
     <font>
@@ -241,7 +239,6 @@
       <sz val="10"/>
       <color indexed="12"/>
       <name val="Times New Roman CE"/>
-      <family val="1"/>
       <charset val="238"/>
     </font>
     <font>
@@ -249,28 +246,24 @@
       <sz val="9"/>
       <color indexed="12"/>
       <name val="Times New Roman CE"/>
-      <family val="1"/>
       <charset val="238"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="12"/>
       <name val="Times New Roman CE"/>
-      <family val="1"/>
       <charset val="238"/>
     </font>
     <font>
       <sz val="9"/>
       <color indexed="12"/>
       <name val="Times New Roman CE"/>
-      <family val="1"/>
       <charset val="238"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="Times New Roman CE"/>
-      <family val="1"/>
       <charset val="238"/>
     </font>
     <font>
@@ -283,7 +276,6 @@
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Times New Roman CE"/>
-      <family val="1"/>
       <charset val="238"/>
     </font>
     <font>
@@ -302,7 +294,6 @@
       <b/>
       <sz val="10"/>
       <name val="Times New Roman CE"/>
-      <family val="1"/>
       <charset val="238"/>
     </font>
     <font>
@@ -310,14 +301,12 @@
       <sz val="11"/>
       <color rgb="FF30A9C6"/>
       <name val="Arial"/>
-      <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
@@ -325,7 +314,6 @@
       <sz val="11"/>
       <color rgb="FF005F8E"/>
       <name val="Arial"/>
-      <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
@@ -339,13 +327,11 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman CE"/>
-      <family val="1"/>
       <charset val="238"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
@@ -366,14 +352,12 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
       <i/>
       <sz val="8"/>
       <name val="Arial"/>
-      <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
@@ -381,14 +365,12 @@
       <i/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
@@ -396,7 +378,6 @@
       <i/>
       <sz val="10"/>
       <name val="Times New Roman CE"/>
-      <family val="1"/>
       <charset val="238"/>
     </font>
     <font>
@@ -404,53 +385,45 @@
       <i/>
       <sz val="7"/>
       <name val="Arial"/>
-      <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="0"/>
       <name val="Times New Roman CE"/>
-      <family val="1"/>
       <charset val="238"/>
     </font>
     <font>
       <i/>
       <sz val="12"/>
       <name val="Times New Roman CE"/>
-      <family val="1"/>
       <charset val="238"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
       <charset val="238"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="Arial"/>
-      <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Arial"/>
-      <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Times New Roman CE"/>
-      <family val="1"/>
       <charset val="238"/>
     </font>
     <font>
@@ -489,7 +462,6 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
@@ -498,7 +470,6 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="Cambria"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="major"/>
     </font>
@@ -507,7 +478,6 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
@@ -516,7 +486,6 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
@@ -525,7 +494,6 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
@@ -534,7 +502,6 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
@@ -542,7 +509,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
@@ -551,7 +517,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
@@ -560,7 +525,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
@@ -569,7 +533,6 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
@@ -577,7 +540,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
@@ -586,7 +548,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
@@ -594,7 +555,6 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
@@ -602,7 +562,6 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
@@ -610,7 +569,6 @@
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
@@ -618,7 +576,6 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
@@ -626,7 +583,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
